--- a/Result/profitability/2457.xlsx
+++ b/Result/profitability/2457.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.19875</v>
+        <v>-0.2675</v>
       </c>
       <c r="N2" t="n">
-        <v>21.39375</v>
+        <v>21.0225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.21625</v>
+        <v>-0.25125</v>
       </c>
       <c r="N3" t="n">
-        <v>19.72875</v>
+        <v>19.665</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.155</v>
+        <v>-0.1525</v>
       </c>
       <c r="N4" t="n">
-        <v>18.55</v>
+        <v>19.1625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07250000000000004</v>
+        <v>-0.01500000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>18.85375</v>
+        <v>19.58875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09124999999999997</v>
+        <v>0.03624999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>20.08875</v>
+        <v>19.90625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1475</v>
+        <v>0.17375</v>
       </c>
       <c r="N7" t="n">
-        <v>19.93</v>
+        <v>20.26125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.99</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3362499999999999</v>
+        <v>0.34</v>
       </c>
       <c r="N8" t="n">
-        <v>20.43625</v>
+        <v>20.77125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.04</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5087499999999999</v>
+        <v>0.50875</v>
       </c>
       <c r="N9" t="n">
         <v>21.12625</v>
@@ -2026,7 +2026,7 @@
         <v>0.78</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9737499999999999</v>
+        <v>0.97375</v>
       </c>
       <c r="N13" t="n">
         <v>27.32375</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2457</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2234</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E75" t="n">
+        <v>533</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-107</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-134</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.46375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.08823529411764708</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1265344664778092</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.5974025974025974</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.879999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3270300333704115</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
